--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.67751175916749</v>
+        <v>4.497595660864717</v>
       </c>
       <c r="D2" t="n">
-        <v>16.22656898384231</v>
+        <v>2.636817459874375</v>
       </c>
       <c r="E2" t="n">
-        <v>6.517285263961996</v>
+        <v>1.059058855393824</v>
       </c>
       <c r="F2" t="n">
-        <v>5.076000016978556</v>
+        <v>0.8248500027590153</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.89793110524657</v>
+        <v>3.883413804602567</v>
       </c>
       <c r="D3" t="n">
-        <v>16.83992984594816</v>
+        <v>2.736488599966576</v>
       </c>
       <c r="E3" t="n">
-        <v>6.517285263961996</v>
+        <v>1.059058855393824</v>
       </c>
       <c r="F3" t="n">
-        <v>5.076000016978556</v>
+        <v>0.8248500027590153</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.2361067735439</v>
+        <v>3.613367350700883</v>
       </c>
       <c r="D4" t="n">
-        <v>23.61984256312162</v>
+        <v>3.838224416507263</v>
       </c>
       <c r="E4" t="n">
-        <v>6.517285263961996</v>
+        <v>1.059058855393824</v>
       </c>
       <c r="F4" t="n">
-        <v>5.076000016978556</v>
+        <v>0.8248500027590153</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.388593697140013</v>
+        <v>1.525646475785252</v>
       </c>
       <c r="D5" t="n">
-        <v>7.684898949745253</v>
+        <v>1.248796079333604</v>
       </c>
       <c r="E5" t="n">
-        <v>6.517285263961996</v>
+        <v>1.059058855393824</v>
       </c>
       <c r="F5" t="n">
-        <v>5.076000016978556</v>
+        <v>0.8248500027590153</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.41544039167016</v>
+        <v>2.5050090636464</v>
       </c>
       <c r="D6" t="n">
-        <v>15.03002253835401</v>
+        <v>2.442378662482527</v>
       </c>
       <c r="E6" t="n">
-        <v>6.517285263961996</v>
+        <v>1.059058855393824</v>
       </c>
       <c r="F6" t="n">
-        <v>5.076000016978556</v>
+        <v>0.8248500027590153</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
